--- a/data/trans_orig/IP31KM07_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM07_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>108956</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>101516</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>113788</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>89,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>83,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>93,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>91116</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>84814</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>95515</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>83,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>117102</t>
+          <t>89438</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98927</t>
+          <t>82854</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124884</t>
+          <t>93714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>208219</t>
+          <t>198394</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>190294</t>
+          <t>189719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217670</t>
+          <t>206181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12253</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7421</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19693</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10593</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6194</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16895</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18074</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36249</t>
+          <t>17495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28667</t>
+          <t>23164</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>31839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>82321</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>76622</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86042</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>91,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>85,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>95,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>86524</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>81233</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>89773</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>92,65%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85817</t>
+          <t>88782</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80093</t>
+          <t>83466</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89681</t>
+          <t>91918</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172341</t>
+          <t>171102</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164695</t>
+          <t>163957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177818</t>
+          <t>176151</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7559</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3838</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13258</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6868</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3619</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12159</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14188</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53047</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48975</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>54941</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>94,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>87,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>44834</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39231</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>48077</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89,51%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>78,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57331</t>
+          <t>47243</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48690</t>
+          <t>42075</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60618</t>
+          <t>50153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>102164</t>
+          <t>100289</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92717</t>
+          <t>94718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107229</t>
+          <t>103849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2797</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6869</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5255</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10858</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>21,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>167929</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>150920</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>178130</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>76,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>173818</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>112044</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>200873</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>80,64%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>51,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>93,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>181202</t>
+          <t>158675</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163539</t>
+          <t>148388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193415</t>
+          <t>165093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>355021</t>
+          <t>326604</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>277770</t>
+          <t>308047</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>385659</t>
+          <t>340371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29384</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19183</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>46393</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>41719</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14664</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>103493</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>48,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31456</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49119</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>73175</t>
+          <t>47349</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42537</t>
+          <t>33582</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150426</t>
+          <t>65906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>123060</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>112008</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>131081</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>84,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>76,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>97830</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>86360</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>104336</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>74,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>134860</t>
+          <t>100572</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124105</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143737</t>
+          <t>105561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>232690</t>
+          <t>223632</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218142</t>
+          <t>211218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>244952</t>
+          <t>234243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22526</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14505</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33578</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>23,06%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>17679</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11173</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>29149</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>15,31%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>25,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24601</t>
+          <t>14894</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35356</t>
+          <t>21281</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>42280</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56828</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>58534</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>51688</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>62582</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>88,87%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>78,48%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>65576</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>61552</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>67681</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>95,18%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>89,34%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60983</t>
+          <t>67018</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54976</t>
+          <t>62429</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65427</t>
+          <t>69388</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>126558</t>
+          <t>125553</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>119776</t>
+          <t>118576</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131516</t>
+          <t>130355</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7329</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3281</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14175</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>21,52%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>3319</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7343</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>17644</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>593846</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>572958</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>611573</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>87,89%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>84,8%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>90,51%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>819</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>559698</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>468747</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>588320</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>86,76%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>72,66%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>637295</t>
+          <t>551729</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>610235</t>
+          <t>537465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>658050</t>
+          <t>563203</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1196992</t>
+          <t>1145575</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1116118</t>
+          <t>1120677</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1233026</t>
+          <t>1166814</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>81849</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>64122</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>102737</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>85433</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>56811</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>176384</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>27,34%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>95073</t>
+          <t>58503</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>74318</t>
+          <t>47029</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>122133</t>
+          <t>72767</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>180507</t>
+          <t>140352</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>144473</t>
+          <t>119113</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>261381</t>
+          <t>165250</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
